--- a/out/Petra Speech Logs 2024-09 and 10 Sept & Oct - 9 weeks 15 sessions, 10-15 SLP absent_log.xlsx
+++ b/out/Petra Speech Logs 2024-09 and 10 Sept & Oct - 9 weeks 15 sessions, 10-15 SLP absent_log.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -528,58 +528,94 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/01/2024</t>
+          <t>09/24/2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10/01/2024</t>
+          <t>09/26/2024</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/08/2024</t>
+          <t>10/01/2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10/08/2024</t>
+          <t>10/01/2024</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/15/2024</t>
+          <t>10/01/2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10/22/2024</t>
+          <t>10/01/2024</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/22/2024</t>
+          <t>10/08/2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10/22/2024</t>
+          <t>10/08/2024</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>10/08/2024</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10/08/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>10/15/2024</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>10/22/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>10/22/2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>10/22/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>10/29/2024</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>10/29/2024</t>
         </is>
